--- a/data/trans_camb/IP7_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP7_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,27</t>
+          <t>-6,77; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,84</t>
+          <t>-6,29; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 35,83</t>
+          <t>-4,15; 37,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 4,01</t>
+          <t>-6,83; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 2,32</t>
+          <t>-7,31; 2,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 11,28</t>
+          <t>-4,77; 9,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,79</t>
+          <t>-5,22; 1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 2,03</t>
+          <t>-5,55; 1,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 19,5</t>
+          <t>-1,67; 19,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-89,0; 96,25</t>
+          <t>-89,22; 112,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,52</t>
+          <t>-100,0; 239,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 2954,55</t>
+          <t>-82,64; 2799,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,71; 162,53</t>
+          <t>-79,84; 239,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,16</t>
+          <t>-100,0; 152,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 423,03</t>
+          <t>-60,7; 337,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 59,55</t>
+          <t>-72,02; 51,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,08; 71,4</t>
+          <t>-81,38; 62,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 682,78</t>
+          <t>-33,43; 634,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,93</t>
+          <t>-0,26; 3,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,07</t>
+          <t>-0,81; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,64</t>
+          <t>-0,48; 2,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,99</t>
+          <t>-2,44; 0,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,55</t>
+          <t>-2,79; 0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,06</t>
+          <t>-3,49; -0,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,37</t>
+          <t>-0,97; 1,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,86</t>
+          <t>-1,4; 0,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,72</t>
+          <t>-1,71; 0,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 312,7</t>
+          <t>-21,93; 321,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 228,99</t>
+          <t>-40,06; 208,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 315,79</t>
+          <t>-30,27; 261,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 43,86</t>
+          <t>-56,06; 48,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 25,07</t>
+          <t>-63,62; 28,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 7,8</t>
+          <t>-78,95; -5,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 70,28</t>
+          <t>-31,14; 71,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 48,83</t>
+          <t>-45,66; 47,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,6; 41,42</t>
+          <t>-53,44; 33,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,82</t>
+          <t>-0,37; 2,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,49</t>
+          <t>-1,07; 1,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,37</t>
+          <t>-0,36; 4,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,03</t>
+          <t>-4,7; 0,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,3</t>
+          <t>-4,69; 0,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,48</t>
+          <t>-2,9; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,04</t>
+          <t>-1,95; 1,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,51</t>
+          <t>-2,35; 0,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,1</t>
+          <t>-0,81; 3,06</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 93,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,2</t>
+          <t>-100,0; 77,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 272,41</t>
+          <t>-70,76; 274,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 178,02</t>
+          <t>-80,98; 184,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-92,07; 58,01</t>
+          <t>-87,49; 60,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 329,1</t>
+          <t>-40,78; 340,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,83</t>
+          <t>-0,54; 1,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,34</t>
+          <t>-1,0; 1,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,69</t>
+          <t>-0,07; 4,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,35</t>
+          <t>-2,49; 0,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; -0,14</t>
+          <t>-2,86; -0,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,36</t>
+          <t>-2,59; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,78</t>
+          <t>-1,11; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,32</t>
+          <t>-1,56; 0,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,53</t>
+          <t>-0,83; 1,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 162,32</t>
+          <t>-27,26; 157,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 117,53</t>
+          <t>-44,5; 113,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 354,01</t>
+          <t>-6,65; 343,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 13,5</t>
+          <t>-56,09; 23,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,09; -3,07</t>
+          <t>-65,97; -1,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 14,73</t>
+          <t>-60,32; 19,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 34,6</t>
+          <t>-35,35; 38,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 15,57</t>
+          <t>-48,73; 13,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 67,85</t>
+          <t>-28,7; 80,38</t>
         </is>
       </c>
     </row>
